--- a/doc/Résultat.xlsx
+++ b/doc/Résultat.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\3Utransat\TUT_EGSE_EP_ads7049_branch\software\G_2_1MSps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\3Utransat\TUT_EGSE_EP_ads7049_branch\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="14235" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="14235" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="@1,1MSps" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>Entrée du filtre(V)</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>erreur sur 16 bits</t>
-  </si>
-  <si>
-    <t>0.02</t>
   </si>
 </sst>
 </file>
@@ -159,7 +156,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -286,11 +282,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="260627976"/>
-        <c:axId val="260628360"/>
+        <c:axId val="249122328"/>
+        <c:axId val="248350232"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="260627976"/>
+        <c:axId val="249122328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -347,12 +343,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260628360"/>
+        <c:crossAx val="248350232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="260628360"/>
+        <c:axId val="248350232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -409,7 +405,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260627976"/>
+        <c:crossAx val="249122328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -503,7 +499,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -630,11 +625,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="260694752"/>
-        <c:axId val="260695136"/>
+        <c:axId val="248428416"/>
+        <c:axId val="248428800"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="260694752"/>
+        <c:axId val="248428416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -691,12 +686,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260695136"/>
+        <c:crossAx val="248428800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="260695136"/>
+        <c:axId val="248428800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -753,7 +748,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260694752"/>
+        <c:crossAx val="248428416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1028,11 +1023,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="260728512"/>
-        <c:axId val="260728896"/>
+        <c:axId val="248480272"/>
+        <c:axId val="248480656"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="260728512"/>
+        <c:axId val="248480272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1089,12 +1084,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260728896"/>
+        <c:crossAx val="248480656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="260728896"/>
+        <c:axId val="248480656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1151,7 +1146,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260728512"/>
+        <c:crossAx val="248480272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1423,11 +1418,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="260830208"/>
-        <c:axId val="260830592"/>
+        <c:axId val="248479736"/>
+        <c:axId val="248593400"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="260830208"/>
+        <c:axId val="248479736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1484,12 +1479,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260830592"/>
+        <c:crossAx val="248593400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="260830592"/>
+        <c:axId val="248593400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1546,7 +1541,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260830208"/>
+        <c:crossAx val="248479736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1815,11 +1810,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="260418808"/>
-        <c:axId val="260416456"/>
+        <c:axId val="245986392"/>
+        <c:axId val="245984040"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="260418808"/>
+        <c:axId val="245986392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1932,12 +1927,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260416456"/>
+        <c:crossAx val="245984040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="260416456"/>
+        <c:axId val="245984040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2050,7 +2045,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260418808"/>
+        <c:crossAx val="245986392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2207,26 +2202,29 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'@1MSps numérisation'!$B$3:$B$8</c:f>
+              <c:f>'@1MSps numérisation'!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>1.5</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>2.5</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>3.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2234,26 +2232,29 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'@1MSps numérisation'!$C$3:$C$8</c:f>
+              <c:f>'@1MSps numérisation'!$C$2:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>3240.0791034937379</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5400.1318391562299</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>10800.26367831246</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>16200.395517468689</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>21600.52735662492</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>27000.659195781147</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>32768</c:v>
                 </c:pt>
               </c:numCache>
@@ -2293,26 +2294,29 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'@1MSps numérisation'!$B$3:$B$8</c:f>
+              <c:f>'@1MSps numérisation'!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>1.5</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>2.5</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>3.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2320,26 +2324,29 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'@1MSps numérisation'!$D$3:$D$8</c:f>
+              <c:f>'@1MSps numérisation'!$D$2:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>2952</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5232</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>10344</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>15700</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>21552</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>26752</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>32760</c:v>
                 </c:pt>
               </c:numCache>
@@ -2355,11 +2362,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="260416848"/>
-        <c:axId val="260413712"/>
+        <c:axId val="248767240"/>
+        <c:axId val="248767632"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="260416848"/>
+        <c:axId val="248767240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2480,12 +2487,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260413712"/>
+        <c:crossAx val="248767632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="260413712"/>
+        <c:axId val="248767632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2598,7 +2605,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="260416848"/>
+        <c:crossAx val="248767240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2817,7 +2824,6 @@
           <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2825,11 +2831,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="145918304"/>
-        <c:axId val="145921048"/>
+        <c:axId val="248770768"/>
+        <c:axId val="248768416"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="145918304"/>
+        <c:axId val="248770768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2942,12 +2948,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="145921048"/>
+        <c:crossAx val="248768416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="145921048"/>
+        <c:axId val="248768416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3060,7 +3066,502 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="145918304"/>
+        <c:crossAx val="248770768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sortie du shaper en fonction de l'entrée</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'@1MSps numérisation'!$A$2:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.255</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'@1MSps numérisation'!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="383785424"/>
+        <c:axId val="383789736"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="383785424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-FR"/>
+                  <a:t>Entrée en Volts</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="383789736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="383789736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-FR"/>
+                  <a:t>Volts</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="383785424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3389,6 +3890,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -6486,6 +7027,522 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7200,16 +8257,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>119061</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>23811</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7223,6 +8280,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2486025</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Graphique 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8218,8 +9305,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
+      <c r="A2" s="1">
+        <v>0.02</v>
       </c>
       <c r="B2">
         <v>0.3</v>
